--- a/Hoàng/2025/T5/CÔNG TY TIN HỌC MỸ VIỆT (81-2025)/DS, DM CÔNG TY TIN HỌC MỸ VIỆT 2025.xlsx
+++ b/Hoàng/2025/T5/CÔNG TY TIN HỌC MỸ VIỆT (81-2025)/DS, DM CÔNG TY TIN HỌC MỸ VIỆT 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\CÔNG TY TIN HỌC VIỆT MỸ (81-2025)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\CÔNG TY TIN HỌC MỸ VIỆT (81-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B237092-CDC6-4BFC-B2F8-AFCF08AF319D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B83B03-8F29-4919-BFE5-ACF05889E29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS" sheetId="1" r:id="rId1"/>
@@ -275,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -298,7 +298,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -854,310 +853,310 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="s">
+      <c r="A8" s="10">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
+      <c r="A13" s="10">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
+      <c r="A14" s="10">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
+      <c r="A15" s="10">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
+      <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
+      <c r="A17" s="10">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
+      <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
+      <c r="A19" s="10">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
+      <c r="A20" s="10">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
+      <c r="A21" s="10">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
+      <c r="A22" s="10">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <v>22</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
+      <c r="A24" s="10">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
+      <c r="A25" s="10">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
+      <c r="A26" s="10">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
+      <c r="A27" s="10">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
+      <c r="A28" s="10">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <v>1</v>
       </c>
     </row>
